--- a/corpus/xlsx/level-019/template.xlsx
+++ b/corpus/xlsx/level-019/template.xlsx
@@ -102,7 +102,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -143,14 +151,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -176,15 +176,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">cu</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">u</t>
     </r>
     <r>
       <rPr>
@@ -200,15 +208,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">om</t>
+      <t xml:space="preserve">to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">m</t>
     </r>
     <r>
       <rPr>
@@ -224,15 +232,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -250,7 +250,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -291,14 +299,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -324,7 +324,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -372,15 +380,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -398,7 +398,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -414,15 +422,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ab</t>
+      <t xml:space="preserve">na</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">b</t>
     </r>
     <r>
       <rPr>
@@ -446,15 +454,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -472,7 +472,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -488,15 +496,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">te</t>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -520,15 +528,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
 </sst>
